--- a/code/b_00_final_kw_v1.xlsx
+++ b/code/b_00_final_kw_v1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/data/a_01_mortality_data_processed/cod_algorithm/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F89E899-41C2-8449-9785-2AB43BF0F347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C8629C-6485-9D45-9720-509122770B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17480" firstSheet="1" activeTab="5" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
   </bookViews>

--- a/code/b_00_final_kw_v1.xlsx
+++ b/code/b_00_final_kw_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C8629C-6485-9D45-9720-509122770B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C06E3C-C399-B241-8255-C9AA8FF9BFF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17480" firstSheet="1" activeTab="5" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" firstSheet="1" activeTab="5" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_names" sheetId="6" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="366">
   <si>
     <t>DIABETES</t>
   </si>
@@ -1057,9 +1057,6 @@
     <t>END STAGE RENAL DISEASE</t>
   </si>
   <si>
-    <t>LIVER FIALURE</t>
-  </si>
-  <si>
     <t>CHRONIC ALCOHOL</t>
   </si>
   <si>
@@ -1115,6 +1112,33 @@
   </si>
   <si>
     <t>CORONAVIRUS</t>
+  </si>
+  <si>
+    <t>DIGESTIVE</t>
+  </si>
+  <si>
+    <t>GENITOUTINARY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENDROCRINE, NUTRITIONAL, AND METABOLIC DISEASE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENDOCRINE </t>
+  </si>
+  <si>
+    <t>KIDNEY DISEASE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIVER FAILURE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIDNEY FAILURE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FATTY LIVER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANCREAS </t>
   </si>
 </sst>
 </file>
@@ -16173,7 +16197,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBEE812F-4599-D14A-8994-D04F411E7319}">
-  <dimension ref="A1:P355"/>
+  <dimension ref="A1:S355"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="21.5" customWidth="1"/>
@@ -16182,16 +16206,19 @@
     <col min="5" max="5" width="21" customWidth="1"/>
     <col min="6" max="6" width="36" customWidth="1"/>
     <col min="7" max="7" width="36.6640625" customWidth="1"/>
-    <col min="8" max="8" width="24.83203125" customWidth="1"/>
+    <col min="8" max="8" width="38.6640625" customWidth="1"/>
     <col min="9" max="10" width="35.33203125" customWidth="1"/>
     <col min="11" max="11" width="37.6640625" customWidth="1"/>
     <col min="12" max="13" width="42.1640625" customWidth="1"/>
     <col min="14" max="14" width="14.83203125" customWidth="1"/>
     <col min="15" max="15" width="16.33203125" customWidth="1"/>
-    <col min="16" max="16" width="16.5" customWidth="1"/>
+    <col min="16" max="16" width="34.6640625" customWidth="1"/>
+    <col min="17" max="17" width="29.33203125" customWidth="1"/>
+    <col min="18" max="18" width="32.33203125" customWidth="1"/>
+    <col min="19" max="19" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>220</v>
       </c>
@@ -16211,7 +16238,7 @@
         <v>322</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>324</v>
@@ -16220,16 +16247,16 @@
         <v>323</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>307</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>18</v>
@@ -16238,10 +16265,19 @@
         <v>221</v>
       </c>
       <c r="P1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>357</v>
+      </c>
+      <c r="R1" t="s">
+        <v>358</v>
+      </c>
+      <c r="S1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>219</v>
       </c>
@@ -16279,7 +16315,7 @@
         <v>216</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>18</v>
@@ -16288,10 +16324,19 @@
         <v>4</v>
       </c>
       <c r="P2" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+        <v>345</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>357</v>
+      </c>
+      <c r="R2" t="s">
+        <v>358</v>
+      </c>
+      <c r="S2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>213</v>
       </c>
@@ -16320,7 +16365,7 @@
         <v>244</v>
       </c>
       <c r="J3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>85</v>
@@ -16329,7 +16374,7 @@
         <v>198</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>1</v>
@@ -16338,10 +16383,19 @@
         <v>42</v>
       </c>
       <c r="P3" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>365</v>
+      </c>
+      <c r="R3" t="s">
+        <v>81</v>
+      </c>
+      <c r="S3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>207</v>
       </c>
@@ -16376,7 +16430,7 @@
         <v>15</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>56</v>
@@ -16384,8 +16438,17 @@
       <c r="O4" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q4" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="R4" t="s">
+        <v>361</v>
+      </c>
+      <c r="S4" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>202</v>
       </c>
@@ -16414,20 +16477,29 @@
         <v>187</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>245</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q5" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="R5" t="s">
+        <v>362</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>196</v>
       </c>
@@ -16456,7 +16528,7 @@
         <v>181</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>190</v>
@@ -16466,8 +16538,17 @@
       <c r="O6" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q6" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="R6" t="s">
+        <v>363</v>
+      </c>
+      <c r="S6" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>192</v>
       </c>
@@ -16489,7 +16570,7 @@
         <v>327</v>
       </c>
       <c r="I7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="7" t="s">
@@ -16500,8 +16581,17 @@
       <c r="O7" s="1" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R7" t="s">
+        <v>364</v>
+      </c>
+      <c r="S7" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>188</v>
       </c>
@@ -16523,7 +16613,7 @@
         <v>328</v>
       </c>
       <c r="I8" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="7" t="s">
@@ -16534,8 +16624,14 @@
       <c r="O8" s="1" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="S8" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>185</v>
       </c>
@@ -16554,7 +16650,7 @@
         <v>257</v>
       </c>
       <c r="I9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="7" t="s">
@@ -16565,8 +16661,11 @@
       <c r="O9" s="1" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R9" s="7" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>179</v>
       </c>
@@ -16599,8 +16698,11 @@
       <c r="O10" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R10" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>176</v>
       </c>
@@ -16633,8 +16735,11 @@
       <c r="O11" s="1" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R11" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>86</v>
       </c>
@@ -16667,8 +16772,11 @@
       <c r="O12" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R12" s="7" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>172</v>
       </c>
@@ -16692,15 +16800,18 @@
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M13" s="7"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R13" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>168</v>
       </c>
@@ -16732,7 +16843,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>165</v>
       </c>
@@ -16764,7 +16875,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>161</v>
       </c>
@@ -16818,7 +16929,7 @@
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="7" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="M17" s="7"/>
       <c r="N17" s="1"/>
@@ -16848,7 +16959,7 @@
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="7" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="M18" s="7"/>
       <c r="N18" s="1"/>
@@ -16878,7 +16989,7 @@
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="7" t="s">
-        <v>39</v>
+        <v>284</v>
       </c>
       <c r="M19" s="7"/>
       <c r="N19" s="1"/>
@@ -16908,7 +17019,7 @@
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="7" t="s">
-        <v>284</v>
+        <v>117</v>
       </c>
       <c r="M20" s="7"/>
       <c r="N20" s="1"/>
@@ -16938,7 +17049,7 @@
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="7" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="M21" s="7"/>
       <c r="N21" s="1"/>
@@ -16968,7 +17079,7 @@
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="7" t="s">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="M22" s="7"/>
       <c r="N22" s="1"/>
@@ -16998,7 +17109,7 @@
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M23" s="7"/>
       <c r="N23" s="1"/>
@@ -17026,7 +17137,7 @@
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="7" t="s">
-        <v>337</v>
+        <v>298</v>
       </c>
       <c r="M24" s="7"/>
       <c r="N24" s="1"/>
@@ -17054,7 +17165,7 @@
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="7" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="M25" s="7"/>
       <c r="N25" s="1"/>
@@ -17079,7 +17190,7 @@
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="7" t="s">
-        <v>298</v>
+        <v>106</v>
       </c>
       <c r="M26" s="7"/>
       <c r="N26" s="1"/>
@@ -17104,7 +17215,7 @@
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="7" t="s">
-        <v>55</v>
+        <v>267</v>
       </c>
       <c r="M27" s="7"/>
       <c r="N27" s="1"/>
@@ -17128,7 +17239,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M28" s="7"/>
       <c r="N28" s="1"/>
@@ -17152,7 +17263,7 @@
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="7" t="s">
-        <v>267</v>
+        <v>102</v>
       </c>
       <c r="M29" s="7"/>
       <c r="N29" s="1"/>
@@ -17176,7 +17287,7 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="7" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="M30" s="7"/>
       <c r="N30" s="1"/>
@@ -17200,7 +17311,7 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="7" t="s">
-        <v>102</v>
+        <v>339</v>
       </c>
       <c r="M31" s="7"/>
       <c r="N31" s="1"/>
@@ -17222,7 +17333,7 @@
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="7" t="s">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="M32" s="7"/>
       <c r="N32" s="1"/>
@@ -17235,14 +17346,16 @@
       <c r="B33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
+      <c r="F33" s="7" t="s">
+        <v>294</v>
+      </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="7" t="s">
-        <v>37</v>
+        <v>256</v>
       </c>
       <c r="M33" s="7"/>
       <c r="N33" s="1"/>
@@ -17256,14 +17369,16 @@
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
+      <c r="F34" s="1" t="s">
+        <v>280</v>
+      </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="7" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="M34" s="7"/>
       <c r="N34" s="1"/>
@@ -17277,14 +17392,16 @@
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
+      <c r="F35" s="7" t="s">
+        <v>71</v>
+      </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="7" t="s">
-        <v>274</v>
+        <v>84</v>
       </c>
       <c r="M35" s="7"/>
       <c r="N35" s="1"/>
@@ -17298,14 +17415,16 @@
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
+      <c r="F36" s="7" t="s">
+        <v>70</v>
+      </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="7" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="M36" s="7"/>
       <c r="N36" s="1"/>
@@ -17326,7 +17445,7 @@
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="7" t="s">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="M37" s="7"/>
       <c r="N37" s="1"/>
@@ -17347,7 +17466,7 @@
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="7" t="s">
-        <v>340</v>
+        <v>32</v>
       </c>
       <c r="M38" s="7"/>
       <c r="N38" s="1"/>
@@ -17368,7 +17487,7 @@
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="7" t="s">
-        <v>282</v>
+        <v>64</v>
       </c>
       <c r="M39" s="7"/>
       <c r="N39" s="1"/>
@@ -17389,7 +17508,7 @@
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="7" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="M40" s="7"/>
       <c r="N40" s="1"/>
@@ -17410,7 +17529,7 @@
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="7" t="s">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="M41" s="7"/>
       <c r="N41" s="1"/>
@@ -17431,7 +17550,7 @@
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="7" t="s">
-        <v>299</v>
+        <v>74</v>
       </c>
       <c r="M42" s="7"/>
       <c r="N42" s="1"/>
@@ -17452,7 +17571,7 @@
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="7" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="M43" s="7"/>
       <c r="N43" s="1"/>
@@ -17473,7 +17592,7 @@
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
       <c r="L44" s="7" t="s">
-        <v>256</v>
+        <v>62</v>
       </c>
       <c r="M44" s="7"/>
       <c r="N44" s="1"/>
@@ -17494,7 +17613,7 @@
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
       <c r="L45" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M45" s="7"/>
       <c r="N45" s="1"/>
@@ -17514,9 +17633,7 @@
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
-      <c r="L46" s="7" t="s">
-        <v>84</v>
-      </c>
+      <c r="L46" s="7"/>
       <c r="M46" s="7"/>
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
@@ -17535,9 +17652,7 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
-      <c r="L47" s="7" t="s">
-        <v>48</v>
-      </c>
+      <c r="L47" s="1"/>
       <c r="M47" s="7"/>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
@@ -17556,9 +17671,7 @@
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
-      <c r="L48" s="7" t="s">
-        <v>83</v>
-      </c>
+      <c r="L48" s="1"/>
       <c r="M48" s="7"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
@@ -17577,9 +17690,7 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
-      <c r="L49" s="7" t="s">
-        <v>82</v>
-      </c>
+      <c r="L49" s="1"/>
       <c r="M49" s="7"/>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
@@ -17598,9 +17709,7 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
-      <c r="L50" s="7" t="s">
-        <v>81</v>
-      </c>
+      <c r="L50" s="2"/>
       <c r="M50" s="7"/>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
@@ -17618,9 +17727,7 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
-      <c r="L51" s="7" t="s">
-        <v>338</v>
-      </c>
+      <c r="L51" s="1"/>
       <c r="M51" s="7"/>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
@@ -17639,9 +17746,7 @@
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
-      <c r="L52" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="L52" s="1"/>
       <c r="M52" s="7"/>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
@@ -17659,9 +17764,7 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
-      <c r="L53" s="7" t="s">
-        <v>78</v>
-      </c>
+      <c r="L53" s="1"/>
       <c r="M53" s="7"/>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
@@ -17679,9 +17782,7 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
-      <c r="L54" s="7" t="s">
-        <v>300</v>
-      </c>
+      <c r="L54" s="1"/>
       <c r="M54" s="7"/>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
@@ -17700,9 +17801,7 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
-      <c r="L55" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="L55" s="2"/>
       <c r="M55" s="7"/>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
@@ -17721,9 +17820,7 @@
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
-      <c r="L56" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="L56" s="1"/>
       <c r="M56" s="7"/>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
@@ -17742,9 +17839,7 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
-      <c r="L57" s="7" t="s">
-        <v>32</v>
-      </c>
+      <c r="L57" s="1"/>
       <c r="M57" s="7"/>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
@@ -17763,9 +17858,7 @@
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
-      <c r="L58" s="7" t="s">
-        <v>52</v>
-      </c>
+      <c r="L58" s="2"/>
       <c r="M58" s="7"/>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
@@ -17784,9 +17877,7 @@
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
-      <c r="L59" s="7" t="s">
-        <v>64</v>
-      </c>
+      <c r="L59" s="1"/>
       <c r="M59" s="7"/>
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
@@ -17805,9 +17896,7 @@
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
-      <c r="L60" s="7" t="s">
-        <v>7</v>
-      </c>
+      <c r="L60" s="1"/>
       <c r="M60" s="7"/>
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
@@ -17826,9 +17915,7 @@
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
-      <c r="L61" s="7" t="s">
-        <v>20</v>
-      </c>
+      <c r="L61" s="1"/>
       <c r="M61" s="7"/>
       <c r="N61" s="1"/>
       <c r="O61" s="1"/>
@@ -17847,9 +17934,7 @@
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
-      <c r="L62" s="7" t="s">
-        <v>74</v>
-      </c>
+      <c r="L62" s="1"/>
       <c r="M62" s="7"/>
       <c r="N62" s="1"/>
       <c r="O62" s="1"/>
@@ -17868,9 +17953,7 @@
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
-      <c r="L63" s="7" t="s">
-        <v>73</v>
-      </c>
+      <c r="L63" s="1"/>
       <c r="M63" s="7"/>
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>
@@ -17889,9 +17972,7 @@
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
-      <c r="L64" s="7" t="s">
-        <v>72</v>
-      </c>
+      <c r="L64" s="1"/>
       <c r="M64" s="7"/>
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
@@ -17910,9 +17991,7 @@
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
-      <c r="L65" s="7" t="s">
-        <v>62</v>
-      </c>
+      <c r="L65" s="1"/>
       <c r="M65" s="7"/>
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
@@ -17931,9 +18010,7 @@
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
-      <c r="L66" s="7" t="s">
-        <v>71</v>
-      </c>
+      <c r="L66" s="1"/>
       <c r="M66" s="7"/>
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
@@ -17952,9 +18029,7 @@
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
-      <c r="L67" s="7" t="s">
-        <v>70</v>
-      </c>
+      <c r="L67" s="1"/>
       <c r="M67" s="7"/>
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
@@ -17973,9 +18048,7 @@
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
-      <c r="L68" s="7" t="s">
-        <v>67</v>
-      </c>
+      <c r="L68" s="1"/>
       <c r="M68" s="7"/>
       <c r="N68" s="1"/>
       <c r="O68" s="1"/>
@@ -17994,9 +18067,7 @@
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
-      <c r="L69" s="7" t="s">
-        <v>294</v>
-      </c>
+      <c r="L69" s="1"/>
       <c r="M69" s="7"/>
       <c r="N69" s="1"/>
       <c r="O69" s="1"/>
@@ -18015,9 +18086,7 @@
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
-      <c r="L70" s="7" t="s">
-        <v>280</v>
-      </c>
+      <c r="L70" s="1"/>
       <c r="M70" s="7"/>
       <c r="N70" s="1"/>
       <c r="O70" s="1"/>
@@ -18093,7 +18162,7 @@
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
-      <c r="L74" s="2"/>
+      <c r="L74" s="1"/>
       <c r="M74" s="2"/>
       <c r="N74" s="1"/>
       <c r="O74" s="1"/>
@@ -18188,7 +18257,7 @@
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
-      <c r="L79" s="2"/>
+      <c r="L79" s="1"/>
       <c r="M79" s="2"/>
       <c r="N79" s="1"/>
       <c r="O79" s="1"/>
@@ -18245,7 +18314,7 @@
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
-      <c r="L82" s="2"/>
+      <c r="L82" s="1"/>
       <c r="M82" s="2"/>
       <c r="N82" s="1"/>
       <c r="O82" s="1"/>
@@ -22457,7 +22526,6 @@
       <c r="I328" s="1"/>
       <c r="J328" s="1"/>
       <c r="K328" s="1"/>
-      <c r="L328" s="1"/>
       <c r="M328" s="1"/>
       <c r="N328" s="1"/>
       <c r="O328" s="1"/>
@@ -22474,7 +22542,6 @@
       <c r="I329" s="1"/>
       <c r="J329" s="1"/>
       <c r="K329" s="1"/>
-      <c r="L329" s="1"/>
       <c r="M329" s="1"/>
       <c r="N329" s="1"/>
       <c r="O329" s="1"/>
@@ -22491,7 +22558,6 @@
       <c r="I330" s="1"/>
       <c r="J330" s="1"/>
       <c r="K330" s="1"/>
-      <c r="L330" s="1"/>
       <c r="M330" s="1"/>
       <c r="N330" s="1"/>
       <c r="O330" s="1"/>
@@ -22508,7 +22574,6 @@
       <c r="I331" s="1"/>
       <c r="J331" s="1"/>
       <c r="K331" s="1"/>
-      <c r="L331" s="1"/>
       <c r="M331" s="1"/>
       <c r="N331" s="1"/>
       <c r="O331" s="1"/>
@@ -22525,7 +22590,6 @@
       <c r="I332" s="1"/>
       <c r="J332" s="1"/>
       <c r="K332" s="1"/>
-      <c r="L332" s="1"/>
       <c r="M332" s="1"/>
       <c r="N332" s="1"/>
       <c r="O332" s="1"/>
@@ -22542,7 +22606,6 @@
       <c r="I333" s="1"/>
       <c r="J333" s="1"/>
       <c r="K333" s="1"/>
-      <c r="L333" s="1"/>
       <c r="M333" s="1"/>
       <c r="N333" s="1"/>
       <c r="O333" s="1"/>
@@ -22559,7 +22622,6 @@
       <c r="I334" s="1"/>
       <c r="J334" s="1"/>
       <c r="K334" s="1"/>
-      <c r="L334" s="1"/>
       <c r="M334" s="1"/>
       <c r="N334" s="1"/>
       <c r="O334" s="1"/>
@@ -22576,7 +22638,6 @@
       <c r="I335" s="1"/>
       <c r="J335" s="1"/>
       <c r="K335" s="1"/>
-      <c r="L335" s="1"/>
       <c r="M335" s="1"/>
       <c r="N335" s="1"/>
       <c r="O335" s="1"/>
@@ -22593,7 +22654,6 @@
       <c r="I336" s="1"/>
       <c r="J336" s="1"/>
       <c r="K336" s="1"/>
-      <c r="L336" s="1"/>
       <c r="M336" s="1"/>
       <c r="N336" s="1"/>
       <c r="O336" s="1"/>
@@ -22610,7 +22670,6 @@
       <c r="I337" s="1"/>
       <c r="J337" s="1"/>
       <c r="K337" s="1"/>
-      <c r="L337" s="1"/>
       <c r="M337" s="1"/>
       <c r="N337" s="1"/>
       <c r="O337" s="1"/>
@@ -22627,7 +22686,6 @@
       <c r="I338" s="1"/>
       <c r="J338" s="1"/>
       <c r="K338" s="1"/>
-      <c r="L338" s="1"/>
       <c r="M338" s="1"/>
       <c r="N338" s="1"/>
       <c r="O338" s="1"/>
@@ -22644,7 +22702,6 @@
       <c r="I339" s="1"/>
       <c r="J339" s="1"/>
       <c r="K339" s="1"/>
-      <c r="L339" s="1"/>
       <c r="M339" s="1"/>
       <c r="N339" s="1"/>
       <c r="O339" s="1"/>
@@ -22661,7 +22718,6 @@
       <c r="I340" s="1"/>
       <c r="J340" s="1"/>
       <c r="K340" s="1"/>
-      <c r="L340" s="1"/>
       <c r="M340" s="1"/>
       <c r="N340" s="1"/>
       <c r="O340" s="1"/>
@@ -22678,7 +22734,6 @@
       <c r="I341" s="1"/>
       <c r="J341" s="1"/>
       <c r="K341" s="1"/>
-      <c r="L341" s="1"/>
       <c r="M341" s="1"/>
       <c r="N341" s="1"/>
       <c r="O341" s="1"/>
@@ -22695,7 +22750,6 @@
       <c r="I342" s="1"/>
       <c r="J342" s="1"/>
       <c r="K342" s="1"/>
-      <c r="L342" s="1"/>
       <c r="M342" s="1"/>
       <c r="N342" s="1"/>
       <c r="O342" s="1"/>
@@ -22712,7 +22766,6 @@
       <c r="I343" s="1"/>
       <c r="J343" s="1"/>
       <c r="K343" s="1"/>
-      <c r="L343" s="1"/>
       <c r="M343" s="1"/>
       <c r="N343" s="1"/>
       <c r="O343" s="1"/>
@@ -22729,7 +22782,6 @@
       <c r="I344" s="1"/>
       <c r="J344" s="1"/>
       <c r="K344" s="1"/>
-      <c r="L344" s="1"/>
       <c r="M344" s="1"/>
       <c r="N344" s="1"/>
       <c r="O344" s="1"/>
@@ -22746,7 +22798,6 @@
       <c r="I345" s="1"/>
       <c r="J345" s="1"/>
       <c r="K345" s="1"/>
-      <c r="L345" s="1"/>
       <c r="M345" s="1"/>
       <c r="N345" s="1"/>
       <c r="O345" s="1"/>
@@ -22762,7 +22813,6 @@
       <c r="I346" s="1"/>
       <c r="J346" s="1"/>
       <c r="K346" s="1"/>
-      <c r="L346" s="1"/>
       <c r="M346" s="1"/>
       <c r="N346" s="1"/>
       <c r="O346" s="1"/>
@@ -22778,7 +22828,6 @@
       <c r="I347" s="1"/>
       <c r="J347" s="1"/>
       <c r="K347" s="1"/>
-      <c r="L347" s="1"/>
       <c r="M347" s="1"/>
       <c r="N347" s="1"/>
       <c r="O347" s="1"/>
@@ -22794,7 +22843,6 @@
       <c r="I348" s="1"/>
       <c r="J348" s="1"/>
       <c r="K348" s="1"/>
-      <c r="L348" s="1"/>
       <c r="M348" s="1"/>
       <c r="N348" s="1"/>
       <c r="O348" s="1"/>
@@ -22810,7 +22858,6 @@
       <c r="I349" s="1"/>
       <c r="J349" s="1"/>
       <c r="K349" s="1"/>
-      <c r="L349" s="1"/>
       <c r="M349" s="1"/>
       <c r="N349" s="1"/>
     </row>
@@ -22825,7 +22872,6 @@
       <c r="I350" s="1"/>
       <c r="J350" s="1"/>
       <c r="K350" s="1"/>
-      <c r="L350" s="1"/>
       <c r="M350" s="1"/>
       <c r="N350" s="1"/>
     </row>
@@ -22840,7 +22886,6 @@
       <c r="I351" s="1"/>
       <c r="J351" s="1"/>
       <c r="K351" s="1"/>
-      <c r="L351" s="1"/>
       <c r="M351" s="1"/>
       <c r="N351" s="1"/>
     </row>

--- a/code/b_00_final_kw_v1.xlsx
+++ b/code/b_00_final_kw_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrieladaza/Documents/GitHub/harmonized_carceral_mortality_data/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C06E3C-C399-B241-8255-C9AA8FF9BFF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A770CB-3BA8-9B4F-B0BD-B87D4AF9CC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" firstSheet="1" activeTab="5" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
+    <workbookView xWindow="140" yWindow="900" windowWidth="14900" windowHeight="17480" firstSheet="1" activeTab="5" xr2:uid="{A6ED5751-AE0F-B045-AA43-8F95CA62E1A7}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet_names" sheetId="6" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="368">
   <si>
     <t>DIABETES</t>
   </si>
@@ -1120,9 +1120,6 @@
     <t>GENITOUTINARY</t>
   </si>
   <si>
-    <t xml:space="preserve">ENDROCRINE, NUTRITIONAL, AND METABOLIC DISEASE </t>
-  </si>
-  <si>
     <t xml:space="preserve">ENDOCRINE </t>
   </si>
   <si>
@@ -1139,6 +1136,15 @@
   </si>
   <si>
     <t xml:space="preserve">PANCREAS </t>
+  </si>
+  <si>
+    <t>DIGESTIVE KEYWORDS</t>
+  </si>
+  <si>
+    <t>GENITOUTINARY KEYWORDS</t>
+  </si>
+  <si>
+    <t>ENDROCRINE, NUTRITIONAL, AND METABOLIC DISEASE  KEYWORDS</t>
   </si>
 </sst>
 </file>
@@ -16215,7 +16221,7 @@
     <col min="16" max="16" width="34.6640625" customWidth="1"/>
     <col min="17" max="17" width="29.33203125" customWidth="1"/>
     <col min="18" max="18" width="32.33203125" customWidth="1"/>
-    <col min="19" max="19" width="47" customWidth="1"/>
+    <col min="19" max="19" width="58.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="34" x14ac:dyDescent="0.2">
@@ -16268,13 +16274,13 @@
         <v>344</v>
       </c>
       <c r="Q1" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="R1" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="S1" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -16386,13 +16392,13 @@
         <v>346</v>
       </c>
       <c r="Q3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="R3" t="s">
         <v>81</v>
       </c>
       <c r="S3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -16442,7 +16448,7 @@
         <v>274</v>
       </c>
       <c r="R4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="S4" s="7" t="s">
         <v>10</v>
@@ -16493,7 +16499,7 @@
         <v>95</v>
       </c>
       <c r="R5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="S5" s="7" t="s">
         <v>8</v>
@@ -16542,7 +16548,7 @@
         <v>268</v>
       </c>
       <c r="R6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="S6" s="7" t="s">
         <v>72</v>
@@ -16585,7 +16591,7 @@
         <v>30</v>
       </c>
       <c r="R7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="S7" s="7" t="s">
         <v>78</v>
